--- a/5/search/FY5_Missile1_results/best_solution.xlsx
+++ b/5/search/FY5_Missile1_results/best_solution.xlsx
@@ -487,37 +487,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135</v>
+        <v>94.5</v>
       </c>
       <c r="B2" t="n">
-        <v>128.8</v>
+        <v>126</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>11542.79434533076</v>
+        <v>12841.82646301267</v>
       </c>
       <c r="F2" t="n">
-        <v>-542.7943453307626</v>
+        <v>9.785344805985915</v>
       </c>
       <c r="G2" t="n">
         <v>1300</v>
       </c>
       <c r="H2" t="n">
-        <v>10996.3422248298</v>
+        <v>12841.82646301267</v>
       </c>
       <c r="I2" t="n">
-        <v>3.657775170201489</v>
+        <v>9.785344805985915</v>
       </c>
       <c r="J2" t="n">
-        <v>1123.6</v>
+        <v>1300</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
